--- a/analises/2026-09-23-tanyno-raros-precificacao.xlsx
+++ b/analises/2026-09-23-tanyno-raros-precificacao.xlsx
@@ -11,15 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>Fator sobre A37</t>
   </si>
   <si>
-    <t>Markup</t>
-  </si>
-  <si>
-    <t>Imposto de renda</t>
+    <t>Imposto de renda (sobre a venda)</t>
   </si>
   <si>
     <t>Vinho</t>
@@ -40,7 +37,13 @@
     <t>Custo (A37 × 1,13)</t>
   </si>
   <si>
-    <t>Preço de venda (custo × 1,6)</t>
+    <t>Margem alvo (após IR ÷ custo)</t>
+  </si>
+  <si>
+    <t>Markup sobre o custo (margem ÷ 0,92)</t>
+  </si>
+  <si>
+    <t>Preço de venda</t>
   </si>
   <si>
     <t>IR 8% sobre a venda</t>
@@ -49,7 +52,7 @@
     <t>Venda após IR</t>
   </si>
   <si>
-    <t>Venda após IR ÷ custo</t>
+    <t>Conferência (após IR ÷ custo)</t>
   </si>
   <si>
     <t>CHATEAU PAVIE-DECESSE</t>
@@ -109,7 +112,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -489,15 +492,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="5" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="10" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -513,303 +518,349 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1546.56</v>
+      </c>
+      <c r="F5" s="2">
+        <f>E5*$B$1</f>
+      </c>
+      <c r="G5" s="3">
+        <v>1.33</v>
+      </c>
+      <c r="H5" s="3">
+        <f>G5/(1-$B$2)</f>
+      </c>
+      <c r="I5" s="2">
+        <f>F5*H5</f>
+      </c>
+      <c r="J5" s="2">
+        <f>I5*$B$2</f>
+      </c>
+      <c r="K5" s="2">
+        <f>I5-J5</f>
+      </c>
+      <c r="L5" s="3">
+        <f>K5/F5</f>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>1546.56</v>
+        <v>2695.79</v>
       </c>
       <c r="F6" s="2">
         <f>E6*$B$1</f>
       </c>
-      <c r="G6" s="2">
-        <f>F6*$B$2</f>
-      </c>
-      <c r="H6" s="2">
-        <f>G6*$B$3</f>
+      <c r="G6" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="H6" s="3">
+        <f>G6/(1-$B$2)</f>
       </c>
       <c r="I6" s="2">
-        <f>G6-H6</f>
-      </c>
-      <c r="J6" s="3">
-        <f>I6/F6</f>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <f>F6*H6</f>
+      </c>
+      <c r="J6" s="2">
+        <f>I6*$B$2</f>
+      </c>
+      <c r="K6" s="2">
+        <f>I6-J6</f>
+      </c>
+      <c r="L6" s="3">
+        <f>K6/F6</f>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" s="2">
-        <v>2695.79</v>
+        <v>3014.68</v>
       </c>
       <c r="F7" s="2">
         <f>E7*$B$1</f>
       </c>
-      <c r="G7" s="2">
-        <f>F7*$B$2</f>
-      </c>
-      <c r="H7" s="2">
-        <f>G7*$B$3</f>
+      <c r="G7" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="H7" s="3">
+        <f>G7/(1-$B$2)</f>
       </c>
       <c r="I7" s="2">
-        <f>G7-H7</f>
-      </c>
-      <c r="J7" s="3">
-        <f>I7/F7</f>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <f>F7*H7</f>
+      </c>
+      <c r="J7" s="2">
+        <f>I7*$B$2</f>
+      </c>
+      <c r="K7" s="2">
+        <f>I7-J7</f>
+      </c>
+      <c r="L7" s="3">
+        <f>K7/F7</f>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>3014.68</v>
+        <v>4782.86</v>
       </c>
       <c r="F8" s="2">
         <f>E8*$B$1</f>
       </c>
-      <c r="G8" s="2">
-        <f>F8*$B$2</f>
-      </c>
-      <c r="H8" s="2">
-        <f>G8*$B$3</f>
+      <c r="G8" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="H8" s="3">
+        <f>G8/(1-$B$2)</f>
       </c>
       <c r="I8" s="2">
-        <f>G8-H8</f>
-      </c>
-      <c r="J8" s="3">
-        <f>I8/F8</f>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <f>F8*H8</f>
+      </c>
+      <c r="J8" s="2">
+        <f>I8*$B$2</f>
+      </c>
+      <c r="K8" s="2">
+        <f>I8-J8</f>
+      </c>
+      <c r="L8" s="3">
+        <f>K8/F8</f>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" s="2">
-        <v>4782.86</v>
+        <v>4867.7</v>
       </c>
       <c r="F9" s="2">
         <f>E9*$B$1</f>
       </c>
-      <c r="G9" s="2">
-        <f>F9*$B$2</f>
-      </c>
-      <c r="H9" s="2">
-        <f>G9*$B$3</f>
+      <c r="G9" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="H9" s="3">
+        <f>G9/(1-$B$2)</f>
       </c>
       <c r="I9" s="2">
-        <f>G9-H9</f>
-      </c>
-      <c r="J9" s="3">
-        <f>I9/F9</f>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <f>F9*H9</f>
+      </c>
+      <c r="J9" s="2">
+        <f>I9*$B$2</f>
+      </c>
+      <c r="K9" s="2">
+        <f>I9-J9</f>
+      </c>
+      <c r="L9" s="3">
+        <f>K9/F9</f>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>4867.7</v>
+        <v>5111.08</v>
       </c>
       <c r="F10" s="2">
         <f>E10*$B$1</f>
       </c>
-      <c r="G10" s="2">
-        <f>F10*$B$2</f>
-      </c>
-      <c r="H10" s="2">
-        <f>G10*$B$3</f>
+      <c r="G10" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="H10" s="3">
+        <f>G10/(1-$B$2)</f>
       </c>
       <c r="I10" s="2">
-        <f>G10-H10</f>
-      </c>
-      <c r="J10" s="3">
-        <f>I10/F10</f>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <f>F10*H10</f>
+      </c>
+      <c r="J10" s="2">
+        <f>I10*$B$2</f>
+      </c>
+      <c r="K10" s="2">
+        <f>I10-J10</f>
+      </c>
+      <c r="L10" s="3">
+        <f>K10/F10</f>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>5111.08</v>
+        <v>5192.21</v>
       </c>
       <c r="F11" s="2">
         <f>E11*$B$1</f>
       </c>
-      <c r="G11" s="2">
-        <f>F11*$B$2</f>
-      </c>
-      <c r="H11" s="2">
-        <f>G11*$B$3</f>
+      <c r="G11" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="H11" s="3">
+        <f>G11/(1-$B$2)</f>
       </c>
       <c r="I11" s="2">
-        <f>G11-H11</f>
-      </c>
-      <c r="J11" s="3">
-        <f>I11/F11</f>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <f>F11*H11</f>
+      </c>
+      <c r="J11" s="2">
+        <f>I11*$B$2</f>
+      </c>
+      <c r="K11" s="2">
+        <f>I11-J11</f>
+      </c>
+      <c r="L11" s="3">
+        <f>K11/F11</f>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" s="2">
-        <v>5192.21</v>
+        <v>7386.05</v>
       </c>
       <c r="F12" s="2">
         <f>E12*$B$1</f>
       </c>
-      <c r="G12" s="2">
-        <f>F12*$B$2</f>
-      </c>
-      <c r="H12" s="2">
-        <f>G12*$B$3</f>
+      <c r="G12" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="H12" s="3">
+        <f>G12/(1-$B$2)</f>
       </c>
       <c r="I12" s="2">
-        <f>G12-H12</f>
-      </c>
-      <c r="J12" s="3">
-        <f>I12/F12</f>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2">
-        <v>7386.05</v>
-      </c>
-      <c r="F13" s="2">
-        <f>E13*$B$1</f>
-      </c>
-      <c r="G13" s="2">
-        <f>F13*$B$2</f>
-      </c>
-      <c r="H13" s="2">
-        <f>G13*$B$3</f>
-      </c>
-      <c r="I13" s="2">
-        <f>G13-H13</f>
-      </c>
-      <c r="J13" s="3">
-        <f>I13/F13</f>
+        <f>F12*H12</f>
+      </c>
+      <c r="J12" s="2">
+        <f>I12*$B$2</f>
+      </c>
+      <c r="K12" s="2">
+        <f>I12-J12</f>
+      </c>
+      <c r="L12" s="3">
+        <f>K12/F12</f>
       </c>
     </row>
   </sheetData>
